--- a/artfynd/A 35214-2025 artfynd.xlsx
+++ b/artfynd/A 35214-2025 artfynd.xlsx
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128755690</v>
+        <v>128757790</v>
       </c>
       <c r="B2" t="n">
-        <v>57847</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gölpan, Gölpan, Sm</t>
+          <t>Solhem, Solhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595241</v>
+        <v>595188</v>
       </c>
       <c r="R2" t="n">
-        <v>6389176</v>
+        <v>6389971</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,49 +791,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128756821</v>
+        <v>128756830</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Karlslund, Karlslund, Sm</t>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,27 +898,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128756830</v>
+        <v>128755690</v>
       </c>
       <c r="B4" t="n">
-        <v>58059</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,16 +927,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karlslund, Karlslund, Sm</t>
+          <t>Gölpan, Gölpan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595244</v>
+        <v>595241</v>
       </c>
       <c r="R4" t="n">
-        <v>6389761</v>
+        <v>6389176</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1013,7 @@
         <v>128757192</v>
       </c>
       <c r="B5" t="n">
-        <v>57847</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,57 +1122,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128757790</v>
+        <v>128756821</v>
       </c>
       <c r="B6" t="n">
-        <v>96187</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solhem, Solhem, Sm</t>
+          <t>Karlslund, Karlslund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595188</v>
+        <v>595244</v>
       </c>
       <c r="R6" t="n">
-        <v>6389971</v>
+        <v>6389761</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
